--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,14 +834,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45182.57900015741</v>
+        <v>45215</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="22">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -899,16 +895,6 @@
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="33" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -1031,7 +1017,6 @@
         <v>508</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1044,35 +1029,30 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="22"/>
     <row r="38" ht="16.5" customHeight="1" s="22"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="22">
       <c r="A42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45215</v>
+        <v>45217</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45217</v>
+        <v>45219</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C29" s="29" t="n"/>
       <c r="D29" s="14" t="n">
-        <v>167</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="22">
@@ -966,7 +966,7 @@
       </c>
       <c r="C30" s="29" t="n"/>
       <c r="D30" s="14" t="n">
-        <v>167</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="22">
@@ -982,7 +982,7 @@
       </c>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="14" t="n">
-        <v>167</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="22">
@@ -998,7 +998,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="14" t="n">
-        <v>167</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1" s="22">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>508</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="22">
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45219</v>
+        <v>45223</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C29" s="29" t="n"/>
       <c r="D29" s="14" t="n">
-        <v>150.3</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="22">
@@ -966,7 +966,7 @@
       </c>
       <c r="C30" s="29" t="n"/>
       <c r="D30" s="14" t="n">
-        <v>150.3</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="22">
@@ -982,7 +982,7 @@
       </c>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="14" t="n">
-        <v>150.3</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="22">
@@ -998,7 +998,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="14" t="n">
-        <v>150.3</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1" s="22">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>457.2</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="22">

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45223</v>
+        <v>45230</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45230</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45232</v>
+        <v>45236</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45236</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1040,19 +1040,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,7 +834,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
+++ b/LISTAS/ma/TOPES ZOCALOS AUTOADHESIVOS DISMAY.xlsx
@@ -834,10 +834,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45266</v>
+        <v>45232.58380520704</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="22">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -895,6 +899,16 @@
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="33" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -950,7 +964,7 @@
       </c>
       <c r="C29" s="29" t="n"/>
       <c r="D29" s="14" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="22">
@@ -966,7 +980,7 @@
       </c>
       <c r="C30" s="29" t="n"/>
       <c r="D30" s="14" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="22">
@@ -982,7 +996,7 @@
       </c>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="14" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="22">
@@ -998,7 +1012,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="14" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1" s="22">
@@ -1014,9 +1028,10 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>508</v>
-      </c>
-    </row>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="22">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1029,30 +1044,35 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="22"/>
     <row r="38" ht="16.5" customHeight="1" s="22"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="22">
       <c r="A42" s="5" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
